--- a/_Drive/Publicacoes/gilberto.xlsx
+++ b/_Drive/Publicacoes/gilberto.xlsx
@@ -4,7 +4,7 @@
   <fileVersion lastEdited="4" lowestEdited="4" rupBuild="3820"/>
   <workbookPr date1904="0"/>
   <bookViews>
-    <workbookView activeTab="0"/>
+    <workbookView activeTab="0" windowWidth="14400" windowHeight="6300"/>
   </bookViews>
   <sheets>
     <sheet name="gilberto.doi" sheetId="1" r:id="rId1"/>
@@ -18,11 +18,38 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="4" count="4">
+  <si>
+    <t>DOI</t>
+  </si>
+  <si>
+    <t>10.1016/j.jallcom.2010.08.019</t>
+  </si>
+  <si>
+    <t>10.1016/j.jmmm.2009.03.067</t>
+  </si>
+  <si>
+    <t>10.1016/j.calphad.2019.101676</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <b val="0"/>
+      <i val="0"/>
+      <u val="none"/>
+      <color rgb="FF000000"/>
+      <name val="Sans"/>
+      <vertAlign val="baseline"/>
+      <sz val="10"/>
+      <strike val="0"/>
+    </font>
+    <font>
+      <b val="1"/>
       <i val="0"/>
       <u val="none"/>
       <color rgb="FF000000"/>
@@ -62,8 +89,12 @@
       <protection locked="1" hidden="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf applyAlignment="1" applyBorder="1" applyFont="1" applyFill="1" applyNumberFormat="1" fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom" wrapText="0" shrinkToFit="0" textRotation="0" indent="0"/>
+      <protection locked="1" hidden="0"/>
+    </xf>
+    <xf applyAlignment="1" applyBorder="1" applyFont="1" applyFill="1" applyNumberFormat="1" fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0">
       <alignment horizontal="general" vertical="bottom" wrapText="0" shrinkToFit="0" textRotation="0" indent="0"/>
       <protection locked="1" hidden="0"/>
     </xf>
@@ -76,567 +107,567 @@
   <sheetPr>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:A80"/>
+  <dimension ref="A1:A81"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="256" style="0" width="9.142307692307693"/>
+    <col min="1" max="1" style="0" width="36.997776442307696" bestFit="1" customWidth="1"/>
+    <col min="2" max="16384" style="0" width="9.142307692307693"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>10.1007/s11669-020-00838-w</t>
-        </is>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>10.1007/s11669-010-9846-x</t>
+          <t>10.1007/s11669-020-00838-w</t>
         </is>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>10.4028/www.scientific.net/msf.805.231</t>
+          <t>10.1007/s11669-010-9846-x</t>
         </is>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>10.4028/www.scientific.net/msf.899.19</t>
+          <t>10.4028/www.scientific.net/msf.805.231</t>
         </is>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10.1590/S1516-14392012005000130</t>
+          <t>10.4028/www.scientific.net/msf.899.19</t>
         </is>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10.1361/105497101770332712</t>
+          <t>10.1590/S1516-14392012005000130</t>
         </is>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>10.1016/j.corsci.2019.108165</t>
+          <t>10.1361/105497101770332712</t>
         </is>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>10.1021/ic401413f</t>
+          <t>10.1016/j.corsci.2019.108165</t>
         </is>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>10.1016/j.jallcom.2003.09.117</t>
+          <t>10.1021/ic401413f</t>
         </is>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>10.1016/j.ijrmhm.2012.04.008</t>
+          <t>10.1016/j.jallcom.2003.09.117</t>
         </is>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>10.1361/15477030418541</t>
+          <t>10.1016/j.ijrmhm.2012.04.008</t>
         </is>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>10.1007/s11669-020-00787-4</t>
+          <t>10.1361/15477030418541</t>
         </is>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>10.4028/www.scientific.net/msf.899.493</t>
+          <t>10.1007/s11669-020-00787-4</t>
         </is>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>10.1016/j.jallcom.2010.08.019</t>
+          <t>10.4028/www.scientific.net/msf.899.493</t>
         </is>
       </c>
     </row>
     <row r="15" spans="1:1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>10.4028/www.scientific.net/MSF.869.423</t>
-        </is>
+      <c r="A15" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>10.1007/s11669-008-9390-0</t>
+          <t>10.4028/www.scientific.net/MSF.869.423</t>
         </is>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>10.1007/s11665-013-0565-4</t>
+          <t>10.1007/s11669-008-9390-0</t>
         </is>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>10.1016/j.intermet.2006.10.054</t>
+          <t>10.1007/s11665-013-0565-4</t>
         </is>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>10.1361/105497103770330758</t>
+          <t>10.1016/j.intermet.2006.10.054</t>
         </is>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>10.1007/s11669-020-00802-8</t>
+          <t>10.1361/105497103770330758</t>
         </is>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>10.1016/j.jallcom.2019.06.186</t>
+          <t>10.1007/s11669-020-00802-8</t>
         </is>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>10.1016/s1003-6326(18)64867-8</t>
+          <t>10.1016/j.jallcom.2019.06.186</t>
         </is>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>10.1590/S1516-14392013005000172</t>
+          <t>10.1016/s1003-6326(18)64867-8</t>
         </is>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>10.1016/j.jssc.2012.02.009</t>
+          <t>10.1590/S1516-14392013005000172</t>
         </is>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>10.1016/S0966-9795(02)00249-2</t>
+          <t>10.1016/j.jssc.2012.02.009</t>
         </is>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>10.1016/j.mtcomm.2020.101282</t>
+          <t>10.1016/S0966-9795(02)00249-2</t>
         </is>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>10.1007/s11669-015-0374-6</t>
+          <t>10.1016/j.mtcomm.2020.101282</t>
         </is>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>10.1016/S0921-5093(02)00604-4</t>
+          <t>10.1007/s11669-015-0374-6</t>
         </is>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>10.1016/j.intermet.2005.05.007</t>
+          <t>10.1016/S0921-5093(02)00604-4</t>
         </is>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>10.1016/j.calphad.2018.08.012</t>
+          <t>10.1016/j.intermet.2005.05.007</t>
         </is>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>10.1007/s11085-020-10013-8</t>
+          <t>10.1016/j.calphad.2018.08.012</t>
         </is>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>10.1016/j.jmmm.2009.03.067</t>
+          <t>10.1007/s11085-020-10013-8</t>
         </is>
       </c>
     </row>
     <row r="33" spans="1:1">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>10.1016/j.matchar.2006.10.020</t>
-        </is>
+      <c r="A33" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>10.1007/s11665-013-0531-1</t>
+          <t>10.1016/j.matchar.2006.10.020</t>
         </is>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>10.1007/s11669-020-00819-z</t>
+          <t>10.1007/s11665-013-0531-1</t>
         </is>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>10.4028/www.scientific.net/msf.805.227</t>
+          <t>10.1007/s11669-020-00819-z</t>
         </is>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>10.1016/j.calphad.2020.102196</t>
+          <t>10.4028/www.scientific.net/msf.805.227</t>
         </is>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>10.1007/s11669-019-00756-6</t>
+          <t>10.1016/j.calphad.2020.102196</t>
         </is>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>10.1016/j.msea.2005.06.003</t>
+          <t>10.1007/s11669-019-00756-6</t>
         </is>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>10.1016/j.matchar.2006.10.015</t>
+          <t>10.1016/j.msea.2005.06.003</t>
         </is>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>10.1016/j.jallcom.2015.11.101</t>
+          <t>10.1016/j.matchar.2006.10.015</t>
         </is>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>10.1007/s11085-014-9517-0</t>
+          <t>10.1016/j.jallcom.2015.11.101</t>
         </is>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>10.1007/s11669-014-0330-x</t>
+          <t>10.1007/s11085-014-9517-0</t>
         </is>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>10.1016/j.calphad.2019.101676</t>
+          <t>10.1007/s11669-014-0330-x</t>
         </is>
       </c>
     </row>
     <row r="45" spans="1:1">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>10.1016/j.jallcom.2018.09.139</t>
-        </is>
+      <c r="A45" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>10.1016/j.surfcoat.2020.125675</t>
+          <t>10.1016/j.jallcom.2018.09.139</t>
         </is>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>10.1590/s1516-14392014005000018</t>
+          <t>10.1016/j.surfcoat.2020.125675</t>
         </is>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>10.1016/j.intermet.2003.09.015</t>
+          <t>10.1590/s1516-14392014005000018</t>
         </is>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>10.1016/j.matchar.2005.09.009</t>
+          <t>10.1016/j.intermet.2003.09.015</t>
         </is>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>10.1016/j.intermet.2006.05.016</t>
+          <t>10.1016/j.matchar.2005.09.009</t>
         </is>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>10.1016/j.calphad.2016.10.005</t>
+          <t>10.1016/j.intermet.2006.05.016</t>
         </is>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>10.1590/S1516-14392012005000015</t>
+          <t>10.1016/j.calphad.2016.10.005</t>
         </is>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>10.1016/j.jssc.2012.01.060</t>
+          <t>10.1590/S1516-14392012005000015</t>
         </is>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>10.1016/j.matchar.2008.04.002</t>
+          <t>10.1016/j.jssc.2012.01.060</t>
         </is>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>10.1016/j.intermet.2004.01.001</t>
+          <t>10.1016/j.matchar.2008.04.002</t>
         </is>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>10.1016/j.matchar.2006.05.014</t>
+          <t>10.1016/j.intermet.2004.01.001</t>
         </is>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>10.1016/j.intermet.2016.04.006</t>
+          <t>10.1016/j.matchar.2006.05.014</t>
         </is>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>10.4028/www.scientific.net/msf.869.58</t>
+          <t>10.1016/j.intermet.2016.04.006</t>
         </is>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>10.1016/j.actamat.2005.04.020</t>
+          <t>10.4028/www.scientific.net/msf.869.58</t>
         </is>
       </c>
     </row>
     <row r="60" spans="1:1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>10.1590/1980-5373-MR-2016-0001</t>
+          <t>10.1016/j.actamat.2005.04.020</t>
         </is>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>10.1016/j.calphad.2017.10.001</t>
+          <t>10.1590/1980-5373-MR-2016-0001</t>
         </is>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>10.1007/s11669-009-9533-y</t>
+          <t>10.1016/j.calphad.2017.10.001</t>
         </is>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>10.1016/j.jallcom.2011.02.042</t>
+          <t>10.1007/s11669-009-9533-y</t>
         </is>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>10.1007/s11661-003-0141-x</t>
+          <t>10.1016/j.jallcom.2011.02.042</t>
         </is>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>10.1007/s11665-013-0814-6</t>
+          <t>10.1007/s11661-003-0141-x</t>
         </is>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>10.1016/j.jallcom.2020.156463</t>
+          <t>10.1007/s11665-013-0814-6</t>
         </is>
       </c>
     </row>
     <row r="67" spans="1:1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>10.1088/0953-2048/28/9/095016</t>
+          <t>10.1016/j.jallcom.2020.156463</t>
         </is>
       </c>
     </row>
     <row r="68" spans="1:1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>10.1007/s11669-015-0418-y</t>
+          <t>10.1088/0953-2048/28/9/095016</t>
         </is>
       </c>
     </row>
     <row r="69" spans="1:1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>10.1007/BF02664849</t>
+          <t>10.1007/s11669-015-0418-y</t>
         </is>
       </c>
     </row>
     <row r="70" spans="1:1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>10.1361/154770306x131976</t>
+          <t>10.1007/BF02664849</t>
         </is>
       </c>
     </row>
     <row r="71" spans="1:1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>10.1590/1980-5373-mr-2019-0305</t>
+          <t>10.1361/154770306x131976</t>
         </is>
       </c>
     </row>
     <row r="72" spans="1:1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>10.1007/s11669-009-9610-2</t>
+          <t>10.1590/1980-5373-mr-2019-0305</t>
         </is>
       </c>
     </row>
     <row r="73" spans="1:1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>10.1016/S1044-5803(01)00176-0</t>
+          <t>10.1007/s11669-009-9610-2</t>
         </is>
       </c>
     </row>
     <row r="74" spans="1:1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>10.1016/j.jallcom.2014.07.026</t>
+          <t>10.1016/S1044-5803(01)00176-0</t>
         </is>
       </c>
     </row>
     <row r="75" spans="1:1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>10.1016/S0966-9795(02)00125-5</t>
+          <t>10.1016/j.jallcom.2014.07.026</t>
         </is>
       </c>
     </row>
     <row r="76" spans="1:1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>10.1016/j.matchar.2005.10.001</t>
+          <t>10.1016/S0966-9795(02)00125-5</t>
         </is>
       </c>
     </row>
     <row r="77" spans="1:1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>10.1016/j.jallcom.2013.04.070</t>
+          <t>10.1016/j.matchar.2005.10.001</t>
         </is>
       </c>
     </row>
     <row r="78" spans="1:1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>10.1016/j.matchar.2012.11.006</t>
+          <t>10.1016/j.jallcom.2013.04.070</t>
         </is>
       </c>
     </row>
     <row r="79" spans="1:1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>10.4028/www.scientific.net/jmnm.20-21.201</t>
+          <t>10.1016/j.matchar.2012.11.006</t>
         </is>
       </c>
     </row>
     <row r="80" spans="1:1">
       <c r="A80" t="inlineStr">
+        <is>
+          <t>10.4028/www.scientific.net/jmnm.20-21.201</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" spans="1:1">
+      <c r="A81" t="inlineStr">
         <is>
           <t>10.1016/j.intermet.2009.03.006</t>
         </is>
